--- a/AdvanceCRM/AdvanceCRM.Web/Templates/MasterSupression_Template.xlsx
+++ b/AdvanceCRM/AdvanceCRM.Web/Templates/MasterSupression_Template.xlsx
@@ -12,18 +12,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t>CampaignId</t>
+    <t>Sr No</t>
   </si>
   <si>
-    <t>CompanyName</t>
+    <t>Account Number</t>
   </si>
   <si>
-    <t>FirstName</t>
+    <t>Company Name</t>
   </si>
   <si>
-    <t>LastName</t>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Last Name</t>
   </si>
   <si>
     <t>Email</t>
@@ -84,16 +87,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.329084396362305" customWidth="1"/>
-    <col min="2" max="2" width="14.488309860229492" customWidth="1"/>
-    <col min="3" max="3" width="9.923392295837402" customWidth="1"/>
-    <col min="4" max="4" width="9.6134033203125" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -118,6 +122,9 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <headerFooter/>

--- a/AdvanceCRM/AdvanceCRM.Web/Templates/MasterSupression_Template.xlsx
+++ b/AdvanceCRM/AdvanceCRM.Web/Templates/MasterSupression_Template.xlsx
@@ -12,12 +12,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Sr No</t>
   </si>
   <si>
     <t>Account Number</t>
+  </si>
+  <si>
+    <t>Campaign Id</t>
   </si>
   <si>
     <t>Company Name</t>
@@ -87,7 +90,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -98,6 +101,7 @@
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -125,6 +129,9 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <headerFooter/>

--- a/AdvanceCRM/AdvanceCRM.Web/Templates/MasterSupression_Template.xlsx
+++ b/AdvanceCRM/AdvanceCRM.Web/Templates/MasterSupression_Template.xlsx
@@ -17,10 +17,10 @@
     <t>Sr No</t>
   </si>
   <si>
-    <t>Account Number</t>
+    <t>Master Account ID</t>
   </si>
   <si>
-    <t>Campaign Id</t>
+    <t>Campaign ID</t>
   </si>
   <si>
     <t>Company Name</t>
